--- a/public/templates/catalog-import-02.xlsx
+++ b/public/templates/catalog-import-02.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R30f810a804ec4bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_压接接头" sheetId="2" r:id="R5d10cde76c014927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R416f071d9a80482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R93a5a9dc74a14ee6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rd5ff2c604b054eda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_压接接头" sheetId="2" r:id="R78255719bbc24f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R90506049a3c143c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Rc0356fa6c90e4f3e"/>
   </x:sheets>
 </x:workbook>
 </file>
